--- a/accounts/ansh/lavanya/train.xlsx
+++ b/accounts/ansh/lavanya/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d7c6e1cda691612/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{4842E9F5-7970-4A55-B298-E17F5B3EA2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB5E37B1-0F86-45D9-B7F8-DA7511C55AFD}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{EC72E8E7-23A0-4E9E-AD11-999E7229CBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21F5B599-614F-478E-B1C7-A1B5875B1E46}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{63DA5A9A-BA5C-41E9-926A-4E5CEEFF429E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="2301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="2370">
   <si>
     <t>DOLA</t>
   </si>
@@ -6937,6 +6937,213 @@
   </si>
   <si>
     <t>MOSS HATHI</t>
+  </si>
+  <si>
+    <t>S2-siroskiblack-1</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-21</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-35</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-31</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-38</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-37</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-34</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-29</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-30</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-13</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-15</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-14</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-25</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-8</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-5</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-41</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-24</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-17</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-39</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-22</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-16</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-23</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-3</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-36</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-7</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-2</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-40</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-4</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-26</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-18</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-12</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-6</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-11</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-19</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-33</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-9</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-1</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-10</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-32</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-42</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-28</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-27</t>
+  </si>
+  <si>
+    <t>S01-Siroskiblack-20</t>
+  </si>
+  <si>
+    <t>S1-siroskiblack-1</t>
+  </si>
+  <si>
+    <t>Siroski</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>S7-sevenstar-4</t>
+  </si>
+  <si>
+    <t>S7-sevenstar-5</t>
+  </si>
+  <si>
+    <t>S7-sevenstar-3</t>
+  </si>
+  <si>
+    <t>S7-sevenstar-2</t>
+  </si>
+  <si>
+    <t>S7-sevenstar-1</t>
+  </si>
+  <si>
+    <t>Seven Star</t>
+  </si>
+  <si>
+    <t>S1-abalaa-1</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-purple-4</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-purple-3</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-purple-2</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-purple-1</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-marun-4</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-marun-3</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-marun-2</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-marun-1</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-wine-4</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-wine-3</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-wine-2</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-wine-1</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-mendi-4</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-mendi-3</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-mendi-2</t>
+  </si>
+  <si>
+    <t>Ss1-mossmirror-mendi-1</t>
   </si>
 </sst>
 </file>
@@ -7318,17 +7525,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FA7E367-A4D9-4DBF-A99F-7A887D13BE14}">
-  <dimension ref="A1:CE332"/>
+  <dimension ref="A1:CG333"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -7337,13 +7549,13 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -7576,25 +7788,31 @@
       <c r="CE1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF1" t="s">
+        <v>2345</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="2" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -7827,25 +8045,31 @@
       <c r="CE2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF2" t="s">
+        <v>2346</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>101</v>
@@ -8078,25 +8302,31 @@
       <c r="CE3" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="4" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF3" s="1" t="s">
+        <v>2301</v>
+      </c>
+      <c r="CG3" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="4" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>184</v>
@@ -8329,25 +8559,31 @@
       <c r="CE4" s="1" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="5" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF4" s="1" t="s">
+        <v>2302</v>
+      </c>
+      <c r="CG4" s="1" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>267</v>
@@ -8580,25 +8816,31 @@
       <c r="CE5" s="1" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="6" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF5" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="CG5" s="1" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>350</v>
@@ -8831,25 +9073,31 @@
       <c r="CE6" s="1" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="7" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF6" s="1" t="s">
+        <v>2304</v>
+      </c>
+      <c r="CG6" s="1" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>433</v>
@@ -9082,19 +9330,25 @@
       <c r="CE7" s="1" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="8" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF7" s="1" t="s">
+        <v>2305</v>
+      </c>
+      <c r="CG7" s="1" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="8" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>514</v>
@@ -9327,19 +9581,22 @@
       <c r="CE8" s="1" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="9" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF8" s="1" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>595</v>
@@ -9500,19 +9757,22 @@
       <c r="CE9" s="1" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="10" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF9" s="1" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>651</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>652</v>
@@ -9670,19 +9930,22 @@
       <c r="CD10" s="1" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="11" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF10" s="1" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>707</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>708</v>
@@ -9840,19 +10103,22 @@
       <c r="CD11" s="1" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="12" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF11" s="1" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="12" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>764</v>
@@ -10010,19 +10276,22 @@
       <c r="CD12" s="1" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="13" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF12" s="1" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>819</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>820</v>
@@ -10180,19 +10449,22 @@
       <c r="CD13" s="1" t="s">
         <v>871</v>
       </c>
-    </row>
-    <row r="14" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF13" s="1" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>875</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>876</v>
@@ -10347,19 +10619,22 @@
       <c r="CD14" s="1" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="15" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF14" s="1" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>930</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>931</v>
@@ -10478,19 +10753,22 @@
       <c r="CD15" s="1" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="16" spans="1:83" x14ac:dyDescent="0.3">
+      <c r="CF15" s="1" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:85" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>972</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>973</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>974</v>
@@ -10609,19 +10887,22 @@
       <c r="CD16" s="1" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="17" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF16" s="1" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>1015</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>1016</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>1017</v>
@@ -10740,19 +11021,22 @@
       <c r="CD17" s="1" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="18" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF17" s="1" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>1058</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>1059</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>1060</v>
@@ -10871,19 +11155,22 @@
       <c r="CD18" s="1" t="s">
         <v>1098</v>
       </c>
-    </row>
-    <row r="19" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF18" s="1" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="19" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>1099</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>1101</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>1102</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>1103</v>
@@ -10999,19 +11286,22 @@
       <c r="CD19" s="1" t="s">
         <v>1140</v>
       </c>
-    </row>
-    <row r="20" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF19" s="1" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>1145</v>
@@ -11127,19 +11417,22 @@
       <c r="CD20" s="1" t="s">
         <v>1182</v>
       </c>
-    </row>
-    <row r="21" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF20" s="1" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="21" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>1185</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>1186</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>1187</v>
@@ -11255,19 +11548,22 @@
       <c r="CD21" s="1" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="22" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF21" s="1" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>1228</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>1229</v>
@@ -11368,19 +11664,22 @@
       <c r="CD22" s="1" t="s">
         <v>1261</v>
       </c>
-    </row>
-    <row r="23" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF22" s="1" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="23" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>1265</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>1266</v>
@@ -11463,19 +11762,22 @@
       <c r="CD23" s="1" t="s">
         <v>1292</v>
       </c>
-    </row>
-    <row r="24" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF23" s="1" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>1296</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>1297</v>
@@ -11540,19 +11842,22 @@
       <c r="AK24" s="1" t="s">
         <v>1317</v>
       </c>
-    </row>
-    <row r="25" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF24" s="1" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="25" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>1320</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>1321</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>1322</v>
@@ -11617,19 +11922,22 @@
       <c r="AK25" s="1" t="s">
         <v>1342</v>
       </c>
-    </row>
-    <row r="26" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF25" s="1" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="26" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>1343</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>1345</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>1346</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>1347</v>
@@ -11691,19 +11999,22 @@
       <c r="AD26" s="1" t="s">
         <v>1366</v>
       </c>
-    </row>
-    <row r="27" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF26" s="1" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="27" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>1368</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>1369</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>1370</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>1371</v>
@@ -11765,19 +12076,22 @@
       <c r="AD27" s="1" t="s">
         <v>1390</v>
       </c>
-    </row>
-    <row r="28" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF27" s="1" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>1393</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>1394</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>1395</v>
@@ -11839,19 +12153,22 @@
       <c r="AD28" s="1" t="s">
         <v>1414</v>
       </c>
-    </row>
-    <row r="29" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF28" s="1" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>1416</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>1417</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>1418</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>1419</v>
@@ -11913,19 +12230,22 @@
       <c r="AD29" s="1" t="s">
         <v>1438</v>
       </c>
-    </row>
-    <row r="30" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF29" s="1" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>1441</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>1442</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>1443</v>
@@ -11987,19 +12307,22 @@
       <c r="AD30" s="1" t="s">
         <v>1462</v>
       </c>
-    </row>
-    <row r="31" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF30" s="1" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>1463</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>1465</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>1466</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>1467</v>
@@ -12061,19 +12384,22 @@
       <c r="AD31" s="1" t="s">
         <v>1486</v>
       </c>
-    </row>
-    <row r="32" spans="1:82" x14ac:dyDescent="0.3">
+      <c r="CF31" s="1" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>1487</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>1488</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>1489</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>1490</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>1491</v>
@@ -12135,19 +12461,22 @@
       <c r="AD32" s="1" t="s">
         <v>1510</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF32" s="1" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>1511</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>1512</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>1513</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>1514</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>1515</v>
@@ -12194,19 +12523,22 @@
       <c r="AD33" s="1" t="s">
         <v>1529</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF33" s="1" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>1531</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>1532</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>1533</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>1534</v>
@@ -12253,16 +12585,19 @@
       <c r="AD34" s="1" t="s">
         <v>1548</v>
       </c>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF34" s="1" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>1549</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>1550</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>1551</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>1552</v>
@@ -12297,16 +12632,19 @@
       <c r="Z35" s="1" t="s">
         <v>1562</v>
       </c>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF35" s="1" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>1563</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>1564</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>1565</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>1566</v>
@@ -12341,16 +12679,19 @@
       <c r="Z36" s="1" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF36" s="1" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>1578</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>1579</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>1580</v>
@@ -12385,16 +12726,19 @@
       <c r="Z37" s="1" t="s">
         <v>1590</v>
       </c>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF37" s="1" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>1592</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>1593</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>1594</v>
@@ -12429,16 +12773,19 @@
       <c r="Z38" s="1" t="s">
         <v>1604</v>
       </c>
-    </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF38" s="1" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="39" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>1606</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>1607</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>1608</v>
@@ -12473,16 +12820,19 @@
       <c r="Z39" s="1" t="s">
         <v>1618</v>
       </c>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF39" s="1" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="40" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>1619</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>1620</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>1621</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>1622</v>
@@ -12517,16 +12867,19 @@
       <c r="Z40" s="1" t="s">
         <v>1632</v>
       </c>
-    </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF40" s="1" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>1633</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>1634</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>1635</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>1636</v>
@@ -12561,16 +12914,19 @@
       <c r="Z41" s="1" t="s">
         <v>1646</v>
       </c>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF41" s="1" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>1648</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>1649</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>1650</v>
@@ -12605,16 +12961,19 @@
       <c r="Z42" s="1" t="s">
         <v>1660</v>
       </c>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF42" s="1" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="43" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>1661</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>1662</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>1663</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>1664</v>
@@ -12649,16 +13008,19 @@
       <c r="Z43" s="1" t="s">
         <v>1674</v>
       </c>
-    </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF43" s="1" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="44" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>1675</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>1676</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>1677</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>1678</v>
@@ -12693,16 +13055,19 @@
       <c r="Z44" s="1" t="s">
         <v>1688</v>
       </c>
-    </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF44" s="1" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="45" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>1689</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>1690</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>1691</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>1692</v>
@@ -12737,16 +13102,19 @@
       <c r="Z45" s="1" t="s">
         <v>1702</v>
       </c>
-    </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF45" s="1" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>1704</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>1705</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>1706</v>
@@ -12781,16 +13149,19 @@
       <c r="Z46" s="1" t="s">
         <v>1716</v>
       </c>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="CF46" s="1" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="47" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>1717</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>2297</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>1718</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>1719</v>
@@ -12808,12 +13179,12 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>1724</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>1725</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>1726</v>
@@ -12831,8 +13202,8 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="49" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F49" s="1" t="s">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>1731</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -12851,8 +13222,8 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="50" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F50" s="1" t="s">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>1737</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -12871,8 +13242,8 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="51" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F51" s="1" t="s">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>1743</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -12891,8 +13262,8 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="52" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F52" s="1" t="s">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>1749</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -12911,8 +13282,8 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="53" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F53" s="1" t="s">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>1755</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -12931,8 +13302,8 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="54" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F54" s="1" t="s">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>1761</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -12951,8 +13322,8 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="55" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F55" s="1" t="s">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>1767</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -12971,8 +13342,8 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="56" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F56" s="1" t="s">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>1773</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -12991,8 +13362,8 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="57" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F57" s="1" t="s">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
         <v>1779</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -13011,8 +13382,8 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="58" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F58" s="1" t="s">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>1785</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -13031,8 +13402,8 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="59" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F59" s="1" t="s">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>1791</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -13051,8 +13422,8 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="60" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F60" s="1" t="s">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
         <v>1797</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -13071,8 +13442,8 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="61" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F61" s="1" t="s">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
         <v>1803</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -13091,8 +13462,8 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="62" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F62" s="1" t="s">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>1809</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -13111,8 +13482,8 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="63" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F63" s="1" t="s">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>1815</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -13131,8 +13502,8 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="64" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F64" s="1" t="s">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>1821</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -13151,8 +13522,8 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="65" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F65" s="1" t="s">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>1827</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -13171,8 +13542,8 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="66" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F66" s="1" t="s">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>1833</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -13191,8 +13562,8 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="67" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F67" s="1" t="s">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>1839</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -13211,8 +13582,8 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="68" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F68" s="1" t="s">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>1845</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -13231,8 +13602,8 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="69" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F69" s="1" t="s">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>1851</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -13251,8 +13622,8 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="70" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F70" s="1" t="s">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>1857</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -13271,8 +13642,8 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="71" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F71" s="1" t="s">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
         <v>1863</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -13291,8 +13662,8 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="72" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F72" s="1" t="s">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
         <v>1869</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -13311,8 +13682,8 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="73" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F73" s="1" t="s">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
         <v>1875</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -13331,8 +13702,8 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="74" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F74" s="1" t="s">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
         <v>1881</v>
       </c>
       <c r="G74" s="1" t="s">
@@ -13351,8 +13722,8 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="75" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F75" s="1" t="s">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
         <v>1887</v>
       </c>
       <c r="G75" s="1" t="s">
@@ -13371,8 +13742,8 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="76" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F76" s="1" t="s">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
         <v>1893</v>
       </c>
       <c r="G76" s="1" t="s">
@@ -13391,8 +13762,8 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="77" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F77" s="1" t="s">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>1899</v>
       </c>
       <c r="G77" s="1" t="s">
@@ -13411,8 +13782,8 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="78" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F78" s="1" t="s">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>1905</v>
       </c>
       <c r="G78" s="1" t="s">
@@ -13431,8 +13802,8 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="79" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F79" s="1" t="s">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>1911</v>
       </c>
       <c r="G79" s="1" t="s">
@@ -13451,8 +13822,8 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="80" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F80" s="1" t="s">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>1917</v>
       </c>
       <c r="G80" s="1" t="s">
@@ -13471,8 +13842,8 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="81" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F81" s="1" t="s">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>1923</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -13491,8 +13862,8 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="82" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F82" s="1" t="s">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>1929</v>
       </c>
       <c r="G82" s="1" t="s">
@@ -13511,8 +13882,8 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="83" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F83" s="1" t="s">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
         <v>1935</v>
       </c>
       <c r="G83" s="1" t="s">
@@ -13531,8 +13902,8 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="84" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F84" s="1" t="s">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>1941</v>
       </c>
       <c r="G84" s="1" t="s">
@@ -13551,8 +13922,8 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="85" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F85" s="1" t="s">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>1947</v>
       </c>
       <c r="G85" s="1" t="s">
@@ -13571,8 +13942,8 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="86" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F86" s="1" t="s">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>1953</v>
       </c>
       <c r="G86" s="1" t="s">
@@ -13591,8 +13962,8 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="87" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F87" s="1" t="s">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
         <v>1959</v>
       </c>
       <c r="G87" s="1" t="s">
@@ -13611,8 +13982,8 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="88" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F88" s="1" t="s">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
         <v>1965</v>
       </c>
       <c r="G88" s="1" t="s">
@@ -13631,8 +14002,8 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="89" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F89" s="1" t="s">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>1971</v>
       </c>
       <c r="G89" s="1" t="s">
@@ -13651,8 +14022,8 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="90" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F90" s="1" t="s">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>1977</v>
       </c>
       <c r="G90" s="1" t="s">
@@ -13671,8 +14042,8 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="91" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F91" s="1" t="s">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>1983</v>
       </c>
       <c r="G91" s="1" t="s">
@@ -13691,8 +14062,8 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="92" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F92" s="1" t="s">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
         <v>1989</v>
       </c>
       <c r="G92" s="1" t="s">
@@ -13711,8 +14082,8 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="93" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F93" s="1" t="s">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>1995</v>
       </c>
       <c r="G93" s="1" t="s">
@@ -13731,8 +14102,8 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="94" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F94" s="1" t="s">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>2001</v>
       </c>
       <c r="G94" s="1" t="s">
@@ -13751,8 +14122,8 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="95" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F95" s="1" t="s">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>2007</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -13771,8 +14142,8 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="96" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F96" s="1" t="s">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>2013</v>
       </c>
       <c r="G96" s="1" t="s">
@@ -13791,8 +14162,8 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="97" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F97" s="1" t="s">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="G97" s="1" t="s">
@@ -13811,8 +14182,8 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="98" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F98" s="1" t="s">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>2025</v>
       </c>
       <c r="G98" s="1" t="s">
@@ -13831,8 +14202,8 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="99" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F99" s="1" t="s">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>2031</v>
       </c>
       <c r="G99" s="1" t="s">
@@ -13851,8 +14222,8 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="100" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F100" s="1" t="s">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
         <v>2037</v>
       </c>
       <c r="G100" s="1" t="s">
@@ -13871,8 +14242,8 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="101" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F101" s="1" t="s">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
         <v>2043</v>
       </c>
       <c r="J101" s="1" t="s">
@@ -13888,8 +14259,8 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="102" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F102" s="1" t="s">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
         <v>2048</v>
       </c>
       <c r="J102" s="1" t="s">
@@ -13905,8 +14276,8 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="103" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F103" s="1" t="s">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
         <v>2053</v>
       </c>
       <c r="J103" s="1" t="s">
@@ -13922,8 +14293,8 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="104" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F104" s="1" t="s">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>2058</v>
       </c>
       <c r="J104" s="1" t="s">
@@ -13939,8 +14310,8 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="105" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F105" s="1" t="s">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
         <v>2063</v>
       </c>
       <c r="J105" s="1" t="s">
@@ -13956,8 +14327,8 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="106" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F106" s="1" t="s">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
         <v>2068</v>
       </c>
       <c r="J106" s="1" t="s">
@@ -13973,1134 +14344,1187 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="107" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F107" s="1" t="s">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
         <v>2073</v>
       </c>
-    </row>
-    <row r="108" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F108" s="1" t="s">
+      <c r="J107" s="1" t="s">
+        <v>2358</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>2366</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>2354</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
         <v>2074</v>
       </c>
-    </row>
-    <row r="109" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F109" s="1" t="s">
+      <c r="J108" s="1" t="s">
+        <v>2359</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>2367</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
         <v>2075</v>
       </c>
-    </row>
-    <row r="110" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F110" s="1" t="s">
+      <c r="J109" s="1" t="s">
+        <v>2360</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>2368</v>
+      </c>
+      <c r="M109" s="1" t="s">
+        <v>2356</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
         <v>2076</v>
       </c>
-    </row>
-    <row r="111" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F111" s="1" t="s">
+      <c r="J110" s="1" t="s">
+        <v>2361</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>2369</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>2357</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
         <v>2077</v>
       </c>
     </row>
-    <row r="112" spans="6:15" x14ac:dyDescent="0.3">
-      <c r="F112" s="1" t="s">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
         <v>2078</v>
       </c>
     </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F113" s="1" t="s">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
         <v>2079</v>
       </c>
     </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F114" s="1" t="s">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
         <v>2080</v>
       </c>
     </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F115" s="1" t="s">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
         <v>2081</v>
       </c>
     </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F116" s="1" t="s">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
         <v>2082</v>
       </c>
     </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F117" s="1" t="s">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
         <v>2083</v>
       </c>
     </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F118" s="1" t="s">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
         <v>2084</v>
       </c>
     </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F119" s="1" t="s">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
         <v>2085</v>
       </c>
     </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F120" s="1" t="s">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
         <v>2086</v>
       </c>
     </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F121" s="1" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
         <v>2087</v>
       </c>
     </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F122" s="1" t="s">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
         <v>2088</v>
       </c>
     </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F123" s="1" t="s">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
         <v>2089</v>
       </c>
     </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F124" s="1" t="s">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
         <v>2090</v>
       </c>
     </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F125" s="1" t="s">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
         <v>2091</v>
       </c>
     </row>
-    <row r="126" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F126" s="1" t="s">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
         <v>2092</v>
       </c>
     </row>
-    <row r="127" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F127" s="1" t="s">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
         <v>2093</v>
       </c>
     </row>
-    <row r="128" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F128" s="1" t="s">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
         <v>2094</v>
       </c>
     </row>
-    <row r="129" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F129" s="1" t="s">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
         <v>2095</v>
       </c>
     </row>
-    <row r="130" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F130" s="1" t="s">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
         <v>2096</v>
       </c>
     </row>
-    <row r="131" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F131" s="1" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
         <v>2097</v>
       </c>
     </row>
-    <row r="132" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F132" s="1" t="s">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
         <v>2098</v>
       </c>
     </row>
-    <row r="133" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F133" s="1" t="s">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
         <v>2099</v>
       </c>
     </row>
-    <row r="134" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F134" s="1" t="s">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
         <v>2100</v>
       </c>
     </row>
-    <row r="135" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F135" s="1" t="s">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
         <v>2101</v>
       </c>
     </row>
-    <row r="136" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F136" s="1" t="s">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
         <v>2102</v>
       </c>
     </row>
-    <row r="137" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F137" s="1" t="s">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
         <v>2103</v>
       </c>
     </row>
-    <row r="138" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F138" s="1" t="s">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
         <v>2104</v>
       </c>
     </row>
-    <row r="139" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F139" s="1" t="s">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
         <v>2105</v>
       </c>
     </row>
-    <row r="140" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F140" s="1" t="s">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
         <v>2106</v>
       </c>
     </row>
-    <row r="141" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F141" s="1" t="s">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
         <v>2107</v>
       </c>
     </row>
-    <row r="142" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F142" s="1" t="s">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
         <v>2108</v>
       </c>
     </row>
-    <row r="143" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F143" s="1" t="s">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
         <v>2109</v>
       </c>
     </row>
-    <row r="144" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F144" s="1" t="s">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="145" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F145" s="1" t="s">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
         <v>2111</v>
       </c>
     </row>
-    <row r="146" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F146" s="1" t="s">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
         <v>2112</v>
       </c>
     </row>
-    <row r="147" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F147" s="1" t="s">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
         <v>2113</v>
       </c>
     </row>
-    <row r="148" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F148" s="1" t="s">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
         <v>2114</v>
       </c>
     </row>
-    <row r="149" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F149" s="1" t="s">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
         <v>2115</v>
       </c>
     </row>
-    <row r="150" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F150" s="1" t="s">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
         <v>2116</v>
       </c>
     </row>
-    <row r="151" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F151" s="1" t="s">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
         <v>2117</v>
       </c>
     </row>
-    <row r="152" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F152" s="1" t="s">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
         <v>2118</v>
       </c>
     </row>
-    <row r="153" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F153" s="1" t="s">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
         <v>2119</v>
       </c>
     </row>
-    <row r="154" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F154" s="1" t="s">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
         <v>2120</v>
       </c>
     </row>
-    <row r="155" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F155" s="1" t="s">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
         <v>2121</v>
       </c>
     </row>
-    <row r="156" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F156" s="1" t="s">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
         <v>2122</v>
       </c>
     </row>
-    <row r="157" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F157" s="1" t="s">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
         <v>2123</v>
       </c>
     </row>
-    <row r="158" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F158" s="1" t="s">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
         <v>2124</v>
       </c>
     </row>
-    <row r="159" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F159" s="1" t="s">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
         <v>2125</v>
       </c>
     </row>
-    <row r="160" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F160" s="1" t="s">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
         <v>2126</v>
       </c>
     </row>
-    <row r="161" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F161" s="1" t="s">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
         <v>2127</v>
       </c>
     </row>
-    <row r="162" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F162" s="1" t="s">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
         <v>2128</v>
       </c>
     </row>
-    <row r="163" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F163" s="1" t="s">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
         <v>2129</v>
       </c>
     </row>
-    <row r="164" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F164" s="1" t="s">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
         <v>2130</v>
       </c>
     </row>
-    <row r="165" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F165" s="1" t="s">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
         <v>2131</v>
       </c>
     </row>
-    <row r="166" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F166" s="1" t="s">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
         <v>2132</v>
       </c>
     </row>
-    <row r="167" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F167" s="1" t="s">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
         <v>2133</v>
       </c>
     </row>
-    <row r="168" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F168" s="1" t="s">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="169" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F169" s="1" t="s">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" s="1" t="s">
         <v>2135</v>
       </c>
     </row>
-    <row r="170" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F170" s="1" t="s">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
         <v>2136</v>
       </c>
     </row>
-    <row r="171" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F171" s="1" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
         <v>2137</v>
       </c>
     </row>
-    <row r="172" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F172" s="1" t="s">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
         <v>2138</v>
       </c>
     </row>
-    <row r="173" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F173" s="1" t="s">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
         <v>2139</v>
       </c>
     </row>
-    <row r="174" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F174" s="1" t="s">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A174" s="1" t="s">
         <v>2140</v>
       </c>
     </row>
-    <row r="175" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F175" s="1" t="s">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
         <v>2141</v>
       </c>
     </row>
-    <row r="176" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F176" s="1" t="s">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
         <v>2142</v>
       </c>
     </row>
-    <row r="177" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F177" s="1" t="s">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
         <v>2143</v>
       </c>
     </row>
-    <row r="178" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F178" s="1" t="s">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
         <v>2144</v>
       </c>
     </row>
-    <row r="179" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F179" s="1" t="s">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
         <v>2145</v>
       </c>
     </row>
-    <row r="180" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F180" s="1" t="s">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
         <v>2146</v>
       </c>
     </row>
-    <row r="181" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F181" s="1" t="s">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
         <v>2147</v>
       </c>
     </row>
-    <row r="182" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F182" s="1" t="s">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
         <v>2148</v>
       </c>
     </row>
-    <row r="183" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F183" s="1" t="s">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
         <v>2149</v>
       </c>
     </row>
-    <row r="184" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F184" s="1" t="s">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
         <v>2150</v>
       </c>
     </row>
-    <row r="185" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F185" s="1" t="s">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
         <v>2151</v>
       </c>
     </row>
-    <row r="186" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F186" s="1" t="s">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
         <v>2152</v>
       </c>
     </row>
-    <row r="187" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F187" s="1" t="s">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
         <v>2153</v>
       </c>
     </row>
-    <row r="188" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F188" s="1" t="s">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A188" s="1" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="189" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F189" s="1" t="s">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
         <v>2155</v>
       </c>
     </row>
-    <row r="190" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F190" s="1" t="s">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
         <v>2156</v>
       </c>
     </row>
-    <row r="191" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F191" s="1" t="s">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
         <v>2157</v>
       </c>
     </row>
-    <row r="192" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F192" s="1" t="s">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A192" s="1" t="s">
         <v>2158</v>
       </c>
     </row>
-    <row r="193" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F193" s="1" t="s">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="1" t="s">
         <v>2159</v>
       </c>
     </row>
-    <row r="194" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F194" s="1" t="s">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A194" s="1" t="s">
         <v>2160</v>
       </c>
     </row>
-    <row r="195" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F195" s="1" t="s">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A195" s="1" t="s">
         <v>2161</v>
       </c>
     </row>
-    <row r="196" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F196" s="1" t="s">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A196" s="1" t="s">
         <v>2162</v>
       </c>
     </row>
-    <row r="197" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F197" s="1" t="s">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A197" s="1" t="s">
         <v>2163</v>
       </c>
     </row>
-    <row r="198" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F198" s="1" t="s">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
         <v>2164</v>
       </c>
     </row>
-    <row r="199" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F199" s="1" t="s">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A199" s="1" t="s">
         <v>2165</v>
       </c>
     </row>
-    <row r="200" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F200" s="1" t="s">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A200" s="1" t="s">
         <v>2166</v>
       </c>
     </row>
-    <row r="201" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F201" s="1" t="s">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A201" s="1" t="s">
         <v>2167</v>
       </c>
     </row>
-    <row r="202" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F202" s="1" t="s">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
         <v>2168</v>
       </c>
     </row>
-    <row r="203" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F203" s="1" t="s">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A203" s="1" t="s">
         <v>2169</v>
       </c>
     </row>
-    <row r="204" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F204" s="1" t="s">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A204" s="1" t="s">
         <v>2170</v>
       </c>
     </row>
-    <row r="205" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F205" s="1" t="s">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A205" s="1" t="s">
         <v>2171</v>
       </c>
     </row>
-    <row r="206" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F206" s="1" t="s">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A206" s="1" t="s">
         <v>2172</v>
       </c>
     </row>
-    <row r="207" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F207" s="1" t="s">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A207" s="1" t="s">
         <v>2173</v>
       </c>
     </row>
-    <row r="208" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F208" s="1" t="s">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A208" s="1" t="s">
         <v>2174</v>
       </c>
     </row>
-    <row r="209" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F209" s="1" t="s">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A209" s="1" t="s">
         <v>2175</v>
       </c>
     </row>
-    <row r="210" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F210" s="1" t="s">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A210" s="1" t="s">
         <v>2176</v>
       </c>
     </row>
-    <row r="211" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F211" s="1" t="s">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A211" s="1" t="s">
         <v>2177</v>
       </c>
     </row>
-    <row r="212" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F212" s="1" t="s">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A212" s="1" t="s">
         <v>2178</v>
       </c>
     </row>
-    <row r="213" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F213" s="1" t="s">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A213" s="1" t="s">
         <v>2179</v>
       </c>
     </row>
-    <row r="214" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F214" s="1" t="s">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A214" s="1" t="s">
         <v>2180</v>
       </c>
     </row>
-    <row r="215" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F215" s="1" t="s">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A215" s="1" t="s">
         <v>2181</v>
       </c>
     </row>
-    <row r="216" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F216" s="1" t="s">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A216" s="1" t="s">
         <v>2182</v>
       </c>
     </row>
-    <row r="217" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F217" s="1" t="s">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="1" t="s">
         <v>2183</v>
       </c>
     </row>
-    <row r="218" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F218" s="1" t="s">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A218" s="1" t="s">
         <v>2184</v>
       </c>
     </row>
-    <row r="219" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F219" s="1" t="s">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A219" s="1" t="s">
         <v>2185</v>
       </c>
     </row>
-    <row r="220" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F220" s="1" t="s">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A220" s="1" t="s">
         <v>2186</v>
       </c>
     </row>
-    <row r="221" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F221" s="1" t="s">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A221" s="1" t="s">
         <v>2187</v>
       </c>
     </row>
-    <row r="222" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F222" s="1" t="s">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A222" s="1" t="s">
         <v>2188</v>
       </c>
     </row>
-    <row r="223" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F223" s="1" t="s">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A223" s="1" t="s">
         <v>2189</v>
       </c>
     </row>
-    <row r="224" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F224" s="1" t="s">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A224" s="1" t="s">
         <v>2190</v>
       </c>
     </row>
-    <row r="225" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F225" s="1" t="s">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
         <v>2191</v>
       </c>
     </row>
-    <row r="226" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F226" s="1" t="s">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
         <v>2192</v>
       </c>
     </row>
-    <row r="227" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F227" s="1" t="s">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
         <v>2193</v>
       </c>
     </row>
-    <row r="228" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F228" s="1" t="s">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
         <v>2194</v>
       </c>
     </row>
-    <row r="229" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F229" s="1" t="s">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
         <v>2195</v>
       </c>
     </row>
-    <row r="230" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F230" s="1" t="s">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
         <v>2196</v>
       </c>
     </row>
-    <row r="231" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F231" s="1" t="s">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A231" s="1" t="s">
         <v>2197</v>
       </c>
     </row>
-    <row r="232" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F232" s="1" t="s">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A232" s="1" t="s">
         <v>2198</v>
       </c>
     </row>
-    <row r="233" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F233" s="1" t="s">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A233" s="1" t="s">
         <v>2199</v>
       </c>
     </row>
-    <row r="234" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F234" s="1" t="s">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A234" s="1" t="s">
         <v>2200</v>
       </c>
     </row>
-    <row r="235" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F235" s="1" t="s">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A235" s="1" t="s">
         <v>2201</v>
       </c>
     </row>
-    <row r="236" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F236" s="1" t="s">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A236" s="1" t="s">
         <v>2202</v>
       </c>
     </row>
-    <row r="237" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F237" s="1" t="s">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A237" s="1" t="s">
         <v>2203</v>
       </c>
     </row>
-    <row r="238" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F238" s="1" t="s">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A238" s="1" t="s">
         <v>2204</v>
       </c>
     </row>
-    <row r="239" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F239" s="1" t="s">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A239" s="1" t="s">
         <v>2205</v>
       </c>
     </row>
-    <row r="240" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F240" s="1" t="s">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A240" s="1" t="s">
         <v>2206</v>
       </c>
     </row>
-    <row r="241" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F241" s="1" t="s">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A241" s="1" t="s">
         <v>2207</v>
       </c>
     </row>
-    <row r="242" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F242" s="1" t="s">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="1" t="s">
         <v>2208</v>
       </c>
     </row>
-    <row r="243" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F243" s="1" t="s">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A243" s="1" t="s">
         <v>2209</v>
       </c>
     </row>
-    <row r="244" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F244" s="1" t="s">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A244" s="1" t="s">
         <v>2210</v>
       </c>
     </row>
-    <row r="245" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F245" s="1" t="s">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A245" s="1" t="s">
         <v>2211</v>
       </c>
     </row>
-    <row r="246" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F246" s="1" t="s">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A246" s="1" t="s">
         <v>2212</v>
       </c>
     </row>
-    <row r="247" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F247" s="1" t="s">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A247" s="1" t="s">
         <v>2213</v>
       </c>
     </row>
-    <row r="248" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F248" s="1" t="s">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A248" s="1" t="s">
         <v>2214</v>
       </c>
     </row>
-    <row r="249" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F249" s="1" t="s">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A249" s="1" t="s">
         <v>2215</v>
       </c>
     </row>
-    <row r="250" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F250" s="1" t="s">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A250" s="1" t="s">
         <v>2216</v>
       </c>
     </row>
-    <row r="251" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F251" s="1" t="s">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A251" s="1" t="s">
         <v>2217</v>
       </c>
     </row>
-    <row r="252" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F252" s="1" t="s">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A252" s="1" t="s">
         <v>2218</v>
       </c>
     </row>
-    <row r="253" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F253" s="1" t="s">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A253" s="1" t="s">
         <v>2219</v>
       </c>
     </row>
-    <row r="254" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F254" s="1" t="s">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A254" s="1" t="s">
         <v>2220</v>
       </c>
     </row>
-    <row r="255" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F255" s="1" t="s">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A255" s="1" t="s">
         <v>2221</v>
       </c>
     </row>
-    <row r="256" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F256" s="1" t="s">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A256" s="1" t="s">
         <v>2222</v>
       </c>
     </row>
-    <row r="257" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F257" s="1" t="s">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A257" s="1" t="s">
         <v>2223</v>
       </c>
     </row>
-    <row r="258" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F258" s="1" t="s">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A258" s="1" t="s">
         <v>2224</v>
       </c>
     </row>
-    <row r="259" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F259" s="1" t="s">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A259" s="1" t="s">
         <v>2225</v>
       </c>
     </row>
-    <row r="260" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F260" s="1" t="s">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
         <v>2226</v>
       </c>
     </row>
-    <row r="261" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F261" s="1" t="s">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A261" s="1" t="s">
         <v>2227</v>
       </c>
     </row>
-    <row r="262" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F262" s="1" t="s">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A262" s="1" t="s">
         <v>2228</v>
       </c>
     </row>
-    <row r="263" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F263" s="1" t="s">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A263" s="1" t="s">
         <v>2229</v>
       </c>
     </row>
-    <row r="264" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F264" s="1" t="s">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A264" s="1" t="s">
         <v>2230</v>
       </c>
     </row>
-    <row r="265" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F265" s="1" t="s">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A265" s="1" t="s">
         <v>2231</v>
       </c>
     </row>
-    <row r="266" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F266" s="1" t="s">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A266" s="1" t="s">
         <v>2232</v>
       </c>
     </row>
-    <row r="267" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F267" s="1" t="s">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A267" s="1" t="s">
         <v>2233</v>
       </c>
     </row>
-    <row r="268" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F268" s="1" t="s">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A268" s="1" t="s">
         <v>2234</v>
       </c>
     </row>
-    <row r="269" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F269" s="1" t="s">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A269" s="1" t="s">
         <v>2235</v>
       </c>
     </row>
-    <row r="270" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F270" s="1" t="s">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A270" s="1" t="s">
         <v>2236</v>
       </c>
     </row>
-    <row r="271" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F271" s="1" t="s">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A271" s="1" t="s">
         <v>2237</v>
       </c>
     </row>
-    <row r="272" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F272" s="1" t="s">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A272" s="1" t="s">
         <v>2238</v>
       </c>
     </row>
-    <row r="273" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F273" s="1" t="s">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A273" s="1" t="s">
         <v>2239</v>
       </c>
     </row>
-    <row r="274" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F274" s="1" t="s">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A274" s="1" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="275" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F275" s="1" t="s">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A275" s="1" t="s">
         <v>2241</v>
       </c>
     </row>
-    <row r="276" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F276" s="1" t="s">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A276" s="1" t="s">
         <v>2242</v>
       </c>
     </row>
-    <row r="277" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F277" s="1" t="s">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="278" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F278" s="1" t="s">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
         <v>2244</v>
       </c>
     </row>
-    <row r="279" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F279" s="1" t="s">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A279" s="1" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="280" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F280" s="1" t="s">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A280" s="1" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="281" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F281" s="1" t="s">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A281" s="1" t="s">
         <v>2247</v>
       </c>
     </row>
-    <row r="282" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F282" s="1" t="s">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A282" s="1" t="s">
         <v>2248</v>
       </c>
     </row>
-    <row r="283" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F283" s="1" t="s">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
         <v>2249</v>
       </c>
     </row>
-    <row r="284" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F284" s="1" t="s">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A284" s="1" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="285" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F285" s="1" t="s">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
         <v>2251</v>
       </c>
     </row>
-    <row r="286" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F286" s="1" t="s">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="287" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F287" s="1" t="s">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A287" s="1" t="s">
         <v>2253</v>
       </c>
     </row>
-    <row r="288" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F288" s="1" t="s">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A288" s="1" t="s">
         <v>2254</v>
       </c>
     </row>
-    <row r="289" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F289" s="1" t="s">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A289" s="1" t="s">
         <v>2255</v>
       </c>
     </row>
-    <row r="290" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F290" s="1" t="s">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
         <v>2256</v>
       </c>
     </row>
-    <row r="291" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F291" s="1" t="s">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291" s="1" t="s">
         <v>2257</v>
       </c>
     </row>
-    <row r="292" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F292" s="1" t="s">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A292" s="1" t="s">
         <v>2258</v>
       </c>
     </row>
-    <row r="293" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F293" s="1" t="s">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A293" s="1" t="s">
         <v>2259</v>
       </c>
     </row>
-    <row r="294" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F294" s="1" t="s">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A294" s="1" t="s">
         <v>2260</v>
       </c>
     </row>
-    <row r="295" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F295" s="1" t="s">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A295" s="1" t="s">
         <v>2261</v>
       </c>
     </row>
-    <row r="296" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F296" s="1" t="s">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A296" s="1" t="s">
         <v>2262</v>
       </c>
     </row>
-    <row r="297" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F297" s="1" t="s">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A297" s="1" t="s">
         <v>2263</v>
       </c>
     </row>
-    <row r="298" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F298" s="1" t="s">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A298" s="1" t="s">
         <v>2264</v>
       </c>
     </row>
-    <row r="299" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F299" s="1" t="s">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A299" s="1" t="s">
         <v>2265</v>
       </c>
     </row>
-    <row r="300" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F300" s="1" t="s">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A300" s="1" t="s">
         <v>2266</v>
       </c>
     </row>
-    <row r="301" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F301" s="1" t="s">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A301" s="1" t="s">
         <v>2267</v>
       </c>
     </row>
-    <row r="302" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F302" s="1" t="s">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A302" s="1" t="s">
         <v>2268</v>
       </c>
     </row>
-    <row r="303" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F303" s="1" t="s">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A303" s="1" t="s">
         <v>2269</v>
       </c>
     </row>
-    <row r="304" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F304" s="1" t="s">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A304" s="1" t="s">
         <v>2270</v>
       </c>
     </row>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F305" s="1" t="s">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A305" s="1" t="s">
         <v>2271</v>
       </c>
     </row>
-    <row r="306" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F306" s="1" t="s">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A306" s="1" t="s">
         <v>2272</v>
       </c>
     </row>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F307" s="1" t="s">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A307" s="1" t="s">
         <v>2273</v>
       </c>
     </row>
-    <row r="308" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F308" s="1" t="s">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A308" s="1" t="s">
         <v>2274</v>
       </c>
     </row>
-    <row r="309" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F309" s="1" t="s">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A309" s="1" t="s">
         <v>2275</v>
       </c>
     </row>
-    <row r="310" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F310" s="1" t="s">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A310" s="1" t="s">
         <v>2276</v>
       </c>
     </row>
-    <row r="311" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F311" s="1" t="s">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A311" s="1" t="s">
         <v>2277</v>
       </c>
     </row>
-    <row r="312" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F312" s="1" t="s">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A312" s="1" t="s">
         <v>2278</v>
       </c>
     </row>
-    <row r="313" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F313" s="1" t="s">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A313" s="1" t="s">
         <v>2279</v>
       </c>
     </row>
-    <row r="314" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F314" s="1" t="s">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A314" s="1" t="s">
         <v>2280</v>
       </c>
     </row>
-    <row r="315" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F315" s="1" t="s">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A315" s="1" t="s">
         <v>2281</v>
       </c>
     </row>
-    <row r="316" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F316" s="1" t="s">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A316" s="1" t="s">
         <v>2282</v>
       </c>
     </row>
-    <row r="317" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F317" s="1" t="s">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A317" s="1" t="s">
         <v>2283</v>
       </c>
     </row>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F318" s="1" t="s">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A318" s="1" t="s">
         <v>2284</v>
       </c>
     </row>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F319" s="1" t="s">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A319" s="1" t="s">
         <v>2285</v>
       </c>
     </row>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F320" s="1" t="s">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A320" s="1" t="s">
         <v>2286</v>
       </c>
     </row>
-    <row r="321" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F321" s="1" t="s">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A321" s="1" t="s">
         <v>2287</v>
       </c>
     </row>
-    <row r="322" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F322" s="1" t="s">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A322" s="1" t="s">
         <v>2288</v>
       </c>
     </row>
-    <row r="323" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F323" s="1" t="s">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A323" s="1" t="s">
         <v>2289</v>
       </c>
     </row>
-    <row r="324" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F324" s="1" t="s">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A324" s="1" t="s">
         <v>2290</v>
       </c>
     </row>
-    <row r="325" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F325" s="1" t="s">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A325" s="1" t="s">
         <v>2291</v>
       </c>
     </row>
-    <row r="326" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F326" s="1" t="s">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A326" s="1" t="s">
         <v>2292</v>
       </c>
     </row>
-    <row r="327" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F327" s="1" t="s">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A327" s="1" t="s">
         <v>2293</v>
       </c>
     </row>
-    <row r="328" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F328" s="1" t="s">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A328" s="1" t="s">
         <v>2294</v>
       </c>
     </row>
-    <row r="329" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F329" s="1" t="s">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A329" s="1" t="s">
         <v>2295</v>
       </c>
     </row>
-    <row r="330" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F330" s="1" t="s">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A330" s="1" t="s">
         <v>2296</v>
       </c>
     </row>
-    <row r="331" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F331" s="1" t="s">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A331" s="1" t="s">
         <v>2298</v>
       </c>
     </row>
-    <row r="332" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F332" s="1" t="s">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A332" s="1" t="s">
         <v>2299</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A333" s="1" t="s">
+        <v>2353</v>
       </c>
     </row>
   </sheetData>
